--- a/Documentación/Pruebas QA.xlsx
+++ b/Documentación/Pruebas QA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Global\Documentación\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5710573A-93EC-48CB-BBAA-4D5258C65372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C521A1-90C2-426F-8A3A-90CD7EF2A994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{2AD847F5-2E81-4705-8C4A-953ADD721B61}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{2AD847F5-2E81-4705-8C4A-953ADD721B61}"/>
   </bookViews>
   <sheets>
     <sheet name="END-REI-IG" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="INC-RENLOT-19" sheetId="6" r:id="rId5"/>
     <sheet name="SIN-1_9" sheetId="7" r:id="rId6"/>
     <sheet name="GLOB-1008" sheetId="8" r:id="rId7"/>
+    <sheet name="GLOB-1010" sheetId="9" r:id="rId8"/>
+    <sheet name="GLOB-1009" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="467">
   <si>
     <t>Prueba</t>
   </si>
@@ -1236,13 +1238,220 @@
   </si>
   <si>
     <t>Al momento de cerrar el reclamo el sistema generó el documento, la información de póliza y reclamo se muestran bien, sin embargo, el sistema no está mostrando el nombre de la cobertura afectada</t>
+  </si>
+  <si>
+    <t>Validar cálculo de prima para Incendio/Rayo/Explosión en operación Nueva</t>
+  </si>
+  <si>
+    <t>Para la operación Nueva, al cumplirse [(Uso_inc == 1)], la prima de Incendio/Rayo/Explosión debe calcularse exactamente con la regla [(cgrupo &gt; -1 ? cgrupo : SA_INC) * (0.105 / 100)].</t>
+  </si>
+  <si>
+    <t>Se validó la póliza, emitiendo el uso particular (1) y se confirmó que la tasa calculada corresponde a la configuración especifica</t>
+  </si>
+  <si>
+    <t>INC-TAR-069</t>
+  </si>
+  <si>
+    <t>Oferta</t>
+  </si>
+  <si>
+    <t>OFER-IN-GL-000495</t>
+  </si>
+  <si>
+    <t>INC-TAR-070</t>
+  </si>
+  <si>
+    <t>Para la operación Nueva, al cumplirse [(Uso_inc == 2)], la prima de Incendio/Rayo/Explosión debe calcularse exactamente con la regla [(cgrupo &gt; -1 ? cgrupo : SA_INC) * (0.14 / 100)].</t>
+  </si>
+  <si>
+    <t>Se validó la póliza, emitiendo el uso Comercial (2) y se confirmó que la tasa calculada corresponde a la configuración especifica</t>
+  </si>
+  <si>
+    <t>Para la operación Nueva, al cumplirse [Uso_inc !== 1 &amp;&amp; Uso_inc !== 2 &amp;&amp; Uso_inc !== 3], la prima de Incendio/Rayo/Explosión debe calcularse exactamente con la regla [0].</t>
+  </si>
+  <si>
+    <t>El sistema al momento de cotizar  un uso que no está en ninguno de los 3 configurados arroja un mensaje indicando que debe asignar un uso válido para calcular</t>
+  </si>
+  <si>
+    <t>INC-TAR-071</t>
+  </si>
+  <si>
+    <t>INC-TAR-072</t>
+  </si>
+  <si>
+    <t>Para la operación Nueva, al cumplirse [(Uso_inc == 3)], la prima de Incendio/Rayo/Explosión debe calcularse exactamente con la regla [(cgrupo &gt; -1 ? cgrupo : SA_INC) * (0.077 / 100)].</t>
+  </si>
+  <si>
+    <t>Se validó la póliza, emitiendo el uso premium (3) y se confirmó que la tasa calculada corresponde a la configuración especifica</t>
+  </si>
+  <si>
+    <t>INC-TAR-073</t>
+  </si>
+  <si>
+    <t>Para la operación Nueva, al cumplirse [(Uso_inc == 1)], la prima de Extensión de Cobertura Catastrófica debe calcularse exactamente con la regla [(cgrupo &gt; -1 ? cgrupo : SA_INC) * (0.045 / 100)].</t>
+  </si>
+  <si>
+    <t>INC-TAR-074</t>
+  </si>
+  <si>
+    <t>Para la operación Nueva, al cumplirse [(Uso_inc == 2)], la prima de Extensión de Cobertura Catastrófica debe calcularse exactamente con la regla [(cgrupo &gt; -1 ? cgrupo : SA_INC) * (0.060 / 100)].</t>
+  </si>
+  <si>
+    <t>INC-TAR-075</t>
+  </si>
+  <si>
+    <t>Para la operación Nueva, al cumplirse [(Uso_inc == 3)], la prima de Extensión de Cobertura Catastrófica debe calcularse exactamente con la regla [(cgrupo &gt; -1 ? cgrupo : SA_INC) * (0.033 / 100)].</t>
+  </si>
+  <si>
+    <t>SIN-1_9-131</t>
+  </si>
+  <si>
+    <t>Validar monto de indemnización en finiquito</t>
+  </si>
+  <si>
+    <t>Se realiza un reclamo y se ejecuta una única reserva y un único pago, generando su respectiva solicitud de pago, luego se procedió a cerrar el reclamo y el sistema generó dos finiquitos, el desestimiento y sin acreedor, el sistema mostró los montos y cobertura correctamente, cuando es único pago</t>
+  </si>
+  <si>
+    <t>SIN-1_9-133</t>
+  </si>
+  <si>
+    <t>Generar finiquito definitivo</t>
+  </si>
+  <si>
+    <t>SIN-1_9-135</t>
+  </si>
+  <si>
+    <t>Reimprimir finiquito</t>
+  </si>
+  <si>
+    <t>El sistema permite volver a generar el reporte de finiquitos sin problemas</t>
+  </si>
+  <si>
+    <t>SIN-1_9-136</t>
+  </si>
+  <si>
+    <t>Generar finiquito antes de aprobación de liquidación</t>
+  </si>
+  <si>
+    <t>El sistema bloquea la emisión definitiva.</t>
+  </si>
+  <si>
+    <t>Bloqueo no existe actualmente en el flujo de trabajo</t>
+  </si>
+  <si>
+    <t>SIN-1_9-137</t>
+  </si>
+  <si>
+    <t>Cerrar reclamo con indemnización y gastos pagados</t>
+  </si>
+  <si>
+    <t>Estado cambia a Cerrado y no quedan reservas abiertas.</t>
+  </si>
+  <si>
+    <t>El sistema al momento del cierre actualiza el estado del reclamo y ejecuta el cierre de los saldos de reserva de manera satisfactoria</t>
+  </si>
+  <si>
+    <t>SIN-1_9-141</t>
+  </si>
+  <si>
+    <t>Consultar trazabilidad completa</t>
+  </si>
+  <si>
+    <t>Se muestran fechas, usuarios, estados y cambios.</t>
+  </si>
+  <si>
+    <t>El reclamo muestra información de flujo de trabajo de manera correcta</t>
+  </si>
+  <si>
+    <t>SIN-PAG-1_9-001</t>
+  </si>
+  <si>
+    <t>Crear solicitud de pago por indemnización</t>
+  </si>
+  <si>
+    <t>La solicitud se genera con número único, estado inicial y vínculo al siniestro y liquidación.</t>
+  </si>
+  <si>
+    <t>Se creó una solicitud de pago única, el sistema muestra la información correcta y se proceda sin problemas</t>
+  </si>
+  <si>
+    <t>SIN-PAG-1_9-002</t>
+  </si>
+  <si>
+    <t>Crear solicitud de pago por gastos</t>
+  </si>
+  <si>
+    <t>La solicitud se genera separada de la indemnización, asociada al gasto y al siniestro.</t>
+  </si>
+  <si>
+    <t>Se creó un pago por gasto y luego se generó su respectiva solicitud de pago, el sistema genera la solicitud sin problemas y esta misma es procesada sin problemas</t>
+  </si>
+  <si>
+    <t>Crear solicitud con varios beneficiarios</t>
+  </si>
+  <si>
+    <t>La suma distribuida coincide con el total solicitado y cada beneficiario queda identificado.</t>
+  </si>
+  <si>
+    <t>El sistema no permite realizar una solicitud de pago con varios beneficiarios, sin embargo, se puede realizar un pago por cada beneficio individualmente</t>
+  </si>
+  <si>
+    <t>SIN-PAG-1_9-004</t>
+  </si>
+  <si>
+    <t>Crear solicitud de pago parcial</t>
+  </si>
+  <si>
+    <t>La solicitud se registra como parcial y mantiene correctamente el saldo pendiente.</t>
+  </si>
+  <si>
+    <t>El sistema permite generar una solicitud de pago con monto parcial sin problemas, se igual manera la solicitud de procesa sin problems</t>
+  </si>
+  <si>
+    <t>SIN-PAG-1_9-005</t>
+  </si>
+  <si>
+    <t>Crear solicitud de pago final</t>
+  </si>
+  <si>
+    <t>La solicitud se identifica como final y deja saldo pendiente en cero al pagarse.</t>
+  </si>
+  <si>
+    <t>SIN-PAG-1_9-006</t>
+  </si>
+  <si>
+    <t>Crear solicitud con retención de impuestos</t>
+  </si>
+  <si>
+    <t>Se calculan y muestran monto bruto, retención y monto neto a pagar.</t>
+  </si>
+  <si>
+    <t>Se creó una solicitud de pago aplicando un impuesto, el sistema muestra la información correcta y se procesa sin problemas</t>
+  </si>
+  <si>
+    <t>SIN-PAG-1_9-012</t>
+  </si>
+  <si>
+    <t>Validar cuenta bancaria obligatoria para transferencia</t>
+  </si>
+  <si>
+    <t>No permite continuar sin una cuenta bancaria válida.</t>
+  </si>
+  <si>
+    <t>El Workflow requiere información de la cuenta bancaria como obligatoria antes de poder avanzar con el pago</t>
+  </si>
+  <si>
+    <t>SIN-PAG-1_9-013</t>
+  </si>
+  <si>
+    <t>Antes de poder crear cualquier solicitud de pago el sistema requiere como obligatorio la forma de pago, ya sea cheque, efectivo, etc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1288,6 +1497,12 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1E293B"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -1348,7 +1563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1401,6 +1616,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4364,7 +4582,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="24.75">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -4390,7 +4608,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="24.75">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -7412,4 +7630,811 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEBFA280-4B81-4852-B993-C0CD1EA28EE1}">
+  <dimension ref="A2:H19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="50.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" customWidth="1"/>
+    <col min="5" max="5" width="40.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="49" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" ht="16.5">
+      <c r="A2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17.25">
+      <c r="A3" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.5">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="71.25">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="60">
+      <c r="A6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16.5">
+      <c r="A8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.25">
+      <c r="A9" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.5">
+      <c r="A10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="71.25">
+      <c r="A11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="60">
+      <c r="A12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5">
+      <c r="A15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17.25">
+      <c r="A16" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="28.5">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="57">
+      <c r="A18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="45">
+      <c r="A19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>412</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C90220F-42B6-49D5-A3A4-303D2E5BC416}">
+  <dimension ref="A3:I33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="14.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="48.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="65.140625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:9" ht="16.5">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17.25">
+      <c r="A4" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="20">
+        <v>166</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" s="20">
+        <v>166</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="I4" s="20">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.5">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="90">
+      <c r="A7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8"/>
+      <c r="D8" s="2"/>
+      <c r="E8"/>
+      <c r="H8"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9"/>
+      <c r="D9" s="2"/>
+      <c r="E9"/>
+      <c r="H9"/>
+    </row>
+    <row r="10" spans="1:9" ht="16.5">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="21" t="s">
+        <v>427</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17.25">
+      <c r="A11" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="20">
+        <v>166</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="E11" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F11" s="20">
+        <v>166</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="I11" s="20">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="45">
+      <c r="A14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="16.5">
+      <c r="B17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="17.25">
+      <c r="B18" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C18" s="20">
+        <v>166</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F18" s="20">
+        <v>166</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="I18" s="20">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="28.5">
+      <c r="B20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="45">
+      <c r="B21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="16.5">
+      <c r="B23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="21" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="17.25">
+      <c r="B24" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C24" s="20">
+        <v>166</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F24" s="20">
+        <v>166</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="I24" s="20">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="28.5">
+      <c r="B26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="45">
+      <c r="B27" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="16.5">
+      <c r="B29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="17.25">
+      <c r="B30" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C30" s="20">
+        <v>166</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F30" s="20">
+        <v>166</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="I30" s="20">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="45">
+      <c r="B33" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>466</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>